--- a/artfynd/A 34748-2025 artfynd.xlsx
+++ b/artfynd/A 34748-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69300320</v>
+        <v>69300324</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531754.1862948088</v>
+        <v>531761</v>
       </c>
       <c r="R2" t="n">
-        <v>6990236.944656814</v>
+        <v>6990296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +764,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -792,7 +777,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov sälg # Salix caprea</t>
+          <t>1 substratenheter # Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,37 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69300322</v>
+        <v>69300326</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531754.1862948088</v>
+        <v>531591</v>
       </c>
       <c r="R3" t="n">
-        <v>6990236.944656814</v>
+        <v>6990457</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,21 +863,11 @@
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -914,12 +884,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -927,7 +897,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov sälg # Salix caprea</t>
+          <t>1 substratenheter # Hård, grov granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69300325</v>
+        <v>69300323</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -985,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531591.1856535735</v>
+        <v>531754</v>
       </c>
       <c r="R4" t="n">
-        <v>6990456.798967262</v>
+        <v>6990237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,19 +983,9 @@
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1017,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # Hålsälg # Salix caprea</t>
+          <t>1 substratenheter # Grov sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,15 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69300323</v>
+        <v>69300320</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1120,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531754.1862948088</v>
+        <v>531754</v>
       </c>
       <c r="R5" t="n">
-        <v>6990236.944656814</v>
+        <v>6990237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,19 +1103,9 @@
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-06-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,15 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69300326</v>
+        <v>69300325</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1255,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531591.1856535735</v>
+        <v>531591</v>
       </c>
       <c r="R6" t="n">
-        <v>6990456.798967262</v>
+        <v>6990457</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,21 +1223,11 @@
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-06-11</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1319,12 +1244,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1332,7 +1257,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # Hård, grov granlåga # Picea abies</t>
+          <t>1 substratenheter # Hålsälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,15 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69300324</v>
+        <v>118637435</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,34 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnsjön, Jmt</t>
+          <t>Saxflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531760.8800870114</v>
+        <v>531446</v>
       </c>
       <c r="R7" t="n">
-        <v>6990296.002283891</v>
+        <v>6990589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,22 +1340,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,39 +1356,16 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Låga # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1488,12 +1375,7 @@
         <v>118637436</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1587,50 +1469,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118637435</v>
+        <v>69300322</v>
       </c>
       <c r="B9" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Saxflon, Jmt</t>
+          <t>Björnsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>531446</v>
+        <v>531754</v>
       </c>
       <c r="R9" t="n">
-        <v>6990589</v>
+        <v>6990237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1657,12 +1534,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2017-06-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2017-06-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,16 +1550,39 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Grov sälg # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 34748-2025 artfynd.xlsx
+++ b/artfynd/A 34748-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300326</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300323</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300320</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300325</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637435</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637436</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,8 +1626,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>